--- a/artfynd/A 36221-2022 artfynd.xlsx
+++ b/artfynd/A 36221-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36221-2022 artfynd.xlsx
+++ b/artfynd/A 36221-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103433423</v>
+        <v>103433424</v>
       </c>
       <c r="B2" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>990</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541900.6528782276</v>
+        <v>541912</v>
       </c>
       <c r="R2" t="n">
-        <v>7064394.584640211</v>
+        <v>7064380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103433425</v>
+        <v>103433429</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541917.4719456988</v>
+        <v>541799</v>
       </c>
       <c r="R3" t="n">
-        <v>7064331.833356668</v>
+        <v>7064233</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,28 +840,17 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103433435</v>
+        <v>103433430</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541677.3375868024</v>
+        <v>541670</v>
       </c>
       <c r="R4" t="n">
-        <v>7064188.954597274</v>
+        <v>7064232</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,24 +937,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Drapperad sälg men även spridit sig till granar i närheten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103433424</v>
+        <v>103433431</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541911.9525697122</v>
+        <v>541699</v>
       </c>
       <c r="R5" t="n">
-        <v>7064379.656285255</v>
+        <v>7064207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,19 +1034,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103433447</v>
+        <v>103433434</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541876.9007169573</v>
+        <v>541708</v>
       </c>
       <c r="R6" t="n">
-        <v>7064310.451280943</v>
+        <v>7064186</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,19 +1131,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103433450</v>
+        <v>103433445</v>
       </c>
       <c r="B7" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>990</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541902.1114217875</v>
+        <v>541898</v>
       </c>
       <c r="R7" t="n">
-        <v>7064351.586372893</v>
+        <v>7064312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,27 +1228,18 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1353,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103433427</v>
+        <v>103433423</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541762.1502610159</v>
+        <v>541901</v>
       </c>
       <c r="R8" t="n">
-        <v>7064189.631247145</v>
+        <v>7064394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,19 +1326,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,37 +1355,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103433426</v>
+        <v>103433450</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541765.1117911184</v>
+        <v>541902</v>
       </c>
       <c r="R9" t="n">
-        <v>7064200.758025131</v>
+        <v>7064352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,19 +1423,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,37 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103433443</v>
+        <v>103433425</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541737.5490910689</v>
+        <v>541917</v>
       </c>
       <c r="R10" t="n">
-        <v>7064169.348279243</v>
+        <v>7064332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,32 +1520,18 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1694,37 +1550,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103433448</v>
+        <v>103433426</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1734,10 +1585,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541832.4046666108</v>
+        <v>541765</v>
       </c>
       <c r="R11" t="n">
-        <v>7064350.662413415</v>
+        <v>7064201</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,19 +1618,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,37 +1647,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103433434</v>
+        <v>103433427</v>
       </c>
       <c r="B12" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1682,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541708.4596045547</v>
+        <v>541762</v>
       </c>
       <c r="R12" t="n">
-        <v>7064186.260833932</v>
+        <v>7064190</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,19 +1715,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,37 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103433430</v>
+        <v>103433435</v>
       </c>
       <c r="B13" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541669.6659433258</v>
+        <v>541677</v>
       </c>
       <c r="R13" t="n">
-        <v>7064231.873119021</v>
+        <v>7064189</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,19 +1812,14 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Drapperad sälg men även spridit sig till granar i närheten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,37 +1846,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103433431</v>
+        <v>103433443</v>
       </c>
       <c r="B14" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2070,10 +1881,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541699.304177556</v>
+        <v>541737</v>
       </c>
       <c r="R14" t="n">
-        <v>7064206.984669569</v>
+        <v>7064170</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,19 +1914,14 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,37 +1948,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103433445</v>
+        <v>103433447</v>
       </c>
       <c r="B15" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +1983,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541897.7450862031</v>
+        <v>541877</v>
       </c>
       <c r="R15" t="n">
-        <v>7064312.501656658</v>
+        <v>7064310</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,28 +2016,17 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2252,6 +2042,103 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103433448</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>541832</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7064351</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36221-2022 artfynd.xlsx
+++ b/artfynd/A 36221-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433429</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433430</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433434</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433445</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433423</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433450</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1547,6 +1592,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433425</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1644,6 +1694,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433426</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1741,6 +1796,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433427</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1843,6 +1903,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433435</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433443</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433447</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,8 +2214,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103433448</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>